--- a/projects/critical_materials/excel_files/technologies_elec_mi.xlsx
+++ b/projects/critical_materials/excel_files/technologies_elec_mi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E63DDE-D61E-1B46-BE8A-57208339F715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DBF1C3-BF2D-9E45-B825-BF0B60F3C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="36380" windowHeight="19540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="106">
   <si>
     <t>AFC</t>
   </si>
@@ -83,9 +83,6 @@
     <t>HYDRO_DAM</t>
   </si>
   <si>
-    <t>HYDRO_GAS</t>
-  </si>
-  <si>
     <t>HYDRO_GAS_CHP</t>
   </si>
   <si>
@@ -330,13 +327,37 @@
   </si>
   <si>
     <t>CCS</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>CHP</t>
+  </si>
+  <si>
+    <t>World bank</t>
+  </si>
+  <si>
+    <t>Confident data</t>
+  </si>
+  <si>
+    <t>Fairly confident</t>
+  </si>
+  <si>
+    <t>Assumptions made</t>
+  </si>
+  <si>
+    <t>Not confident</t>
+  </si>
+  <si>
+    <t>CCGT considered</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,8 +387,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri (Corps)"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,6 +442,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -439,7 +477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -450,6 +488,11 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -768,27 +811,26 @@
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="20.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -856,7 +898,7 @@
       <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>22</v>
       </c>
       <c r="AB1" t="s">
@@ -883,7 +925,7 @@
       <c r="AI1" t="s">
         <v>30</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>31</v>
       </c>
       <c r="AN1" t="s">
@@ -892,72 +934,73 @@
       <c r="AO1" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AS1" t="s">
         <v>34</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B2" s="6"/>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="I2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="J2" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="K2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="O2" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="P2" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="T2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>73</v>
       </c>
       <c r="X2" s="4" t="s">
@@ -972,20 +1015,22 @@
       <c r="AA2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AB2" s="4" t="s">
-        <v>78</v>
+      <c r="AB2" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD2" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE2" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="AI2" s="4" t="s">
         <v>84</v>
@@ -999,8 +1044,10 @@
       <c r="AL2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AM2" s="4" t="s">
-        <v>88</v>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="AP2" s="4" t="s">
         <v>80</v>
@@ -1012,7 +1059,7 @@
         <v>82</v>
       </c>
       <c r="AS2" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AT2" s="4" t="s">
         <v>74</v>
@@ -1023,16 +1070,16 @@
       <c r="AV2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AW2" s="4" t="s">
-        <v>77</v>
+      <c r="AX2" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="AY2" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>121.125</v>
@@ -1082,8 +1129,12 @@
       <c r="Q3" s="2">
         <v>3400</v>
       </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="R3" s="2">
+        <v>922.2</v>
+      </c>
+      <c r="S3" s="2">
+        <v>3400</v>
+      </c>
       <c r="T3" s="2">
         <v>3400</v>
       </c>
@@ -1094,22 +1145,22 @@
         <v>3400</v>
       </c>
       <c r="W3" s="2">
-        <v>3400</v>
+        <v>700</v>
       </c>
       <c r="X3" s="2">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="Y3" s="2">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="Z3" s="2">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="AA3" s="2">
-        <v>1600</v>
+        <v>61104.4</v>
       </c>
       <c r="AB3" s="2">
-        <v>61104.4</v>
+        <v>922.2</v>
       </c>
       <c r="AC3" s="2">
         <v>922.2</v>
@@ -1120,8 +1171,8 @@
       <c r="AE3" s="2">
         <v>922.2</v>
       </c>
-      <c r="AF3" s="2">
-        <v>922.2</v>
+      <c r="AH3" s="2">
+        <v>10953</v>
       </c>
       <c r="AI3" s="2">
         <v>10953</v>
@@ -1135,32 +1186,32 @@
       <c r="AL3" s="2">
         <v>10953</v>
       </c>
-      <c r="AM3" s="2">
-        <v>10953</v>
+      <c r="AO3" s="2">
+        <v>700</v>
       </c>
       <c r="AP3" s="2">
+        <v>1400</v>
+      </c>
+      <c r="AQ3" s="2">
+        <v>500</v>
+      </c>
+      <c r="AR3" s="2">
+        <v>1600</v>
+      </c>
+      <c r="AS3" s="2">
         <v>700</v>
       </c>
-      <c r="AQ3" s="2">
+      <c r="AT3" s="2">
         <v>1400</v>
       </c>
-      <c r="AR3" s="2">
+      <c r="AU3" s="2">
         <v>500</v>
       </c>
-      <c r="AS3" s="2">
+      <c r="AV3" s="2">
         <v>1600</v>
       </c>
-      <c r="AT3" s="2">
-        <v>700</v>
-      </c>
-      <c r="AU3" s="2">
-        <v>1400</v>
-      </c>
-      <c r="AV3" s="2">
-        <v>500</v>
-      </c>
-      <c r="AW3" s="2">
-        <v>1600</v>
+      <c r="AX3" s="2">
+        <v>0</v>
       </c>
       <c r="AY3" s="2">
         <v>0</v>
@@ -1168,7 +1219,7 @@
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1218,8 +1269,12 @@
       <c r="Q4" s="2">
         <v>0</v>
       </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
       <c r="T4" s="2">
         <v>0</v>
       </c>
@@ -1236,67 +1291,67 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="2">
         <v>6</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AR4" s="2">
         <v>1</v>
       </c>
-      <c r="AB4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="2">
+      <c r="AS4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="2">
         <v>6</v>
       </c>
-      <c r="AS4" s="2">
+      <c r="AV4" s="2">
         <v>1</v>
       </c>
-      <c r="AT4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="2">
-        <v>6</v>
-      </c>
-      <c r="AW4" s="2">
-        <v>1</v>
+      <c r="AX4" s="2">
+        <v>0</v>
       </c>
       <c r="AY4" s="2">
         <v>0</v>
@@ -1304,7 +1359,7 @@
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1354,8 +1409,12 @@
       <c r="Q5" s="2">
         <v>0</v>
       </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
       <c r="T5" s="2">
         <v>0</v>
       </c>
@@ -1378,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AA5" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AB5" s="2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="2">
         <v>0</v>
@@ -1392,22 +1451,22 @@
       <c r="AE5" s="2">
         <v>0</v>
       </c>
-      <c r="AF5" s="2">
+      <c r="AH5" s="2">
         <v>0</v>
       </c>
       <c r="AI5" s="2">
         <v>0</v>
       </c>
       <c r="AJ5" s="2">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AK5" s="2">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="2">
         <v>0</v>
       </c>
-      <c r="AM5" s="2">
+      <c r="AO5" s="2">
         <v>0</v>
       </c>
       <c r="AP5" s="2">
@@ -1431,7 +1490,7 @@
       <c r="AV5" s="2">
         <v>0</v>
       </c>
-      <c r="AW5" s="2">
+      <c r="AX5" s="2">
         <v>0</v>
       </c>
       <c r="AY5" s="2">
@@ -1440,7 +1499,7 @@
     </row>
     <row r="6" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1494,8 +1553,12 @@
       <c r="Q6" s="2">
         <v>1500</v>
       </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="R6" s="2">
+        <v>48.34</v>
+      </c>
+      <c r="S6" s="2">
+        <v>1500</v>
+      </c>
       <c r="T6" s="2">
         <v>1500</v>
       </c>
@@ -1506,22 +1569,22 @@
         <v>1500</v>
       </c>
       <c r="W6" s="2">
-        <v>1500</v>
+        <v>525</v>
       </c>
       <c r="X6" s="2">
+        <v>470</v>
+      </c>
+      <c r="Y6" s="2">
         <v>525</v>
       </c>
-      <c r="Y6" s="2">
-        <v>470</v>
-      </c>
       <c r="Z6" s="2">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="AA6" s="2">
-        <v>580</v>
+        <v>2190</v>
       </c>
       <c r="AB6" s="2">
-        <v>2190</v>
+        <v>48.34</v>
       </c>
       <c r="AC6" s="2">
         <v>48.34</v>
@@ -1532,8 +1595,8 @@
       <c r="AE6" s="2">
         <v>48.34</v>
       </c>
-      <c r="AF6" s="2">
-        <v>48.34</v>
+      <c r="AH6" s="2">
+        <v>3761</v>
       </c>
       <c r="AI6" s="2">
         <v>3761</v>
@@ -1547,40 +1610,40 @@
       <c r="AL6" s="2">
         <v>3761</v>
       </c>
-      <c r="AM6" s="2">
-        <v>3761</v>
+      <c r="AO6" s="2">
+        <v>525</v>
       </c>
       <c r="AP6" s="2">
+        <v>470</v>
+      </c>
+      <c r="AQ6" s="2">
         <v>525</v>
       </c>
-      <c r="AQ6" s="2">
+      <c r="AR6" s="2">
+        <v>580</v>
+      </c>
+      <c r="AS6" s="2">
+        <v>525</v>
+      </c>
+      <c r="AT6" s="2">
         <v>470</v>
       </c>
-      <c r="AR6" s="2">
+      <c r="AU6" s="2">
         <v>525</v>
       </c>
-      <c r="AS6" s="2">
+      <c r="AV6" s="2">
         <v>580</v>
       </c>
-      <c r="AT6" s="2">
-        <v>525</v>
-      </c>
-      <c r="AU6" s="2">
-        <v>470</v>
-      </c>
-      <c r="AV6" s="2">
-        <v>525</v>
-      </c>
-      <c r="AW6" s="2">
-        <v>580</v>
+      <c r="AX6" s="2">
+        <v>326</v>
       </c>
       <c r="AY6" s="2">
-        <v>326</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1632,8 +1695,12 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
       <c r="T7" s="2">
         <v>0</v>
       </c>
@@ -1644,19 +1711,19 @@
         <v>0</v>
       </c>
       <c r="W7" s="2">
-        <v>0</v>
+        <v>1.4285714285714299E-2</v>
       </c>
       <c r="X7" s="2">
-        <v>1.4285714285714299E-2</v>
+        <v>0.553968253968255</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.553968253968255</v>
+        <v>0.2349206349206347</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.2349206349206347</v>
+        <v>0.19682539682539602</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.19682539682539602</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2">
         <v>0</v>
@@ -1670,7 +1737,7 @@
       <c r="AE7" s="2">
         <v>0</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>0</v>
       </c>
       <c r="AI7" s="2">
@@ -1685,7 +1752,7 @@
       <c r="AL7" s="2">
         <v>0</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>0</v>
       </c>
       <c r="AP7" s="2">
@@ -1709,16 +1776,16 @@
       <c r="AV7" s="2">
         <v>0</v>
       </c>
-      <c r="AW7" s="2">
-        <v>0</v>
+      <c r="AX7" s="2">
+        <v>7.5</v>
       </c>
       <c r="AY7" s="2">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1768,8 +1835,12 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
       <c r="T8" s="2">
         <v>0</v>
       </c>
@@ -1780,19 +1851,19 @@
         <v>0</v>
       </c>
       <c r="W8" s="2">
-        <v>0</v>
+        <v>369000</v>
       </c>
       <c r="X8" s="2">
-        <v>369000</v>
+        <v>355000</v>
       </c>
       <c r="Y8" s="2">
-        <v>355000</v>
+        <v>243000</v>
       </c>
       <c r="Z8" s="2">
-        <v>243000</v>
+        <v>413000</v>
       </c>
       <c r="AA8" s="2">
-        <v>413000</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="2">
         <v>0</v>
@@ -1806,8 +1877,8 @@
       <c r="AE8" s="2">
         <v>0</v>
       </c>
-      <c r="AF8" s="2">
-        <v>0</v>
+      <c r="AH8" s="2">
+        <v>60700</v>
       </c>
       <c r="AI8" s="2">
         <v>60700</v>
@@ -1821,32 +1892,32 @@
       <c r="AL8" s="2">
         <v>60700</v>
       </c>
-      <c r="AM8" s="2">
-        <v>60700</v>
+      <c r="AO8" s="2">
+        <v>369000</v>
       </c>
       <c r="AP8" s="2">
+        <v>355000</v>
+      </c>
+      <c r="AQ8" s="2">
+        <v>243000</v>
+      </c>
+      <c r="AR8" s="2">
+        <v>413000</v>
+      </c>
+      <c r="AS8" s="2">
         <v>369000</v>
       </c>
-      <c r="AQ8" s="2">
+      <c r="AT8" s="2">
         <v>355000</v>
       </c>
-      <c r="AR8" s="2">
+      <c r="AU8" s="2">
         <v>243000</v>
       </c>
-      <c r="AS8" s="2">
+      <c r="AV8" s="2">
         <v>413000</v>
       </c>
-      <c r="AT8" s="2">
-        <v>369000</v>
-      </c>
-      <c r="AU8" s="2">
-        <v>355000</v>
-      </c>
-      <c r="AV8" s="2">
-        <v>243000</v>
-      </c>
-      <c r="AW8" s="2">
-        <v>413000</v>
+      <c r="AX8" s="2">
+        <v>0</v>
       </c>
       <c r="AY8" s="2">
         <v>0</v>
@@ -1854,7 +1925,7 @@
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>1226.5</v>
@@ -1910,8 +1981,12 @@
       <c r="Q9" s="2">
         <v>3160</v>
       </c>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+      <c r="R9" s="2">
+        <v>1110</v>
+      </c>
+      <c r="S9" s="2">
+        <v>3160</v>
+      </c>
       <c r="T9" s="2">
         <v>3160</v>
       </c>
@@ -1922,22 +1997,22 @@
         <v>3160</v>
       </c>
       <c r="W9" s="2">
-        <v>3160</v>
+        <v>5000</v>
       </c>
       <c r="X9" s="2">
-        <v>5000</v>
+        <v>1400</v>
       </c>
       <c r="Y9" s="2">
-        <v>1400</v>
+        <v>8000</v>
       </c>
       <c r="Z9" s="2">
-        <v>8000</v>
+        <v>950</v>
       </c>
       <c r="AA9" s="2">
-        <v>950</v>
+        <v>1473.4</v>
       </c>
       <c r="AB9" s="2">
-        <v>1473.4</v>
+        <v>1110</v>
       </c>
       <c r="AC9" s="2">
         <v>1110</v>
@@ -1948,56 +2023,56 @@
       <c r="AE9" s="2">
         <v>1110</v>
       </c>
-      <c r="AF9" s="2">
-        <v>1110</v>
+      <c r="AH9" s="2">
+        <v>3765</v>
       </c>
       <c r="AI9" s="2">
-        <v>3765</v>
+        <f>AH9+AH29</f>
+        <v>3795</v>
       </c>
       <c r="AJ9" s="2">
-        <f>AI9+AI29</f>
-        <v>3795</v>
+        <v>3698.0333333333333</v>
       </c>
       <c r="AK9" s="2">
-        <v>3698.0333333333333</v>
+        <v>3123.42</v>
       </c>
       <c r="AL9" s="2">
-        <v>3123.42</v>
-      </c>
-      <c r="AM9" s="2">
         <v>3187.82</v>
       </c>
+      <c r="AO9" s="2">
+        <v>5000</v>
+      </c>
       <c r="AP9" s="2">
+        <v>1400</v>
+      </c>
+      <c r="AQ9" s="2">
+        <v>8000</v>
+      </c>
+      <c r="AR9" s="2">
+        <v>950</v>
+      </c>
+      <c r="AS9" s="2">
         <v>5000</v>
       </c>
-      <c r="AQ9" s="2">
+      <c r="AT9" s="2">
         <v>1400</v>
       </c>
-      <c r="AR9" s="2">
+      <c r="AU9" s="2">
         <v>8000</v>
       </c>
-      <c r="AS9" s="2">
+      <c r="AV9" s="2">
         <v>950</v>
       </c>
-      <c r="AT9" s="2">
-        <v>5000</v>
-      </c>
-      <c r="AU9" s="2">
-        <v>1400</v>
-      </c>
-      <c r="AV9" s="2">
-        <v>8000</v>
-      </c>
-      <c r="AW9" s="2">
-        <v>950</v>
+      <c r="AX9" s="2">
+        <v>692</v>
       </c>
       <c r="AY9" s="2">
-        <v>692</v>
+        <v>44448</v>
       </c>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2047,8 +2122,12 @@
       <c r="Q10" s="2">
         <v>0</v>
       </c>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
       <c r="T10" s="2">
         <v>0</v>
       </c>
@@ -2059,73 +2138,73 @@
         <v>0</v>
       </c>
       <c r="W10" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X10" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>17</v>
+      </c>
+      <c r="Z10" s="2">
         <v>6</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="AA10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="2">
+        <v>6</v>
+      </c>
+      <c r="AP10" s="2">
         <v>2</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="AQ10" s="2">
         <v>17</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AR10" s="2">
         <v>6</v>
-      </c>
-      <c r="AB10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="2">
-        <v>6</v>
-      </c>
-      <c r="AQ10" s="2">
-        <v>2</v>
-      </c>
-      <c r="AR10" s="2">
-        <v>17</v>
       </c>
       <c r="AS10" s="2">
         <v>6</v>
       </c>
       <c r="AT10" s="2">
+        <v>2</v>
+      </c>
+      <c r="AU10" s="2">
+        <v>17</v>
+      </c>
+      <c r="AV10" s="2">
         <v>6</v>
       </c>
-      <c r="AU10" s="2">
-        <v>2</v>
-      </c>
-      <c r="AV10" s="2">
-        <v>17</v>
-      </c>
-      <c r="AW10" s="2">
-        <v>6</v>
+      <c r="AX10" s="2">
+        <v>0</v>
       </c>
       <c r="AY10" s="2">
         <v>0</v>
@@ -2133,7 +2212,7 @@
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2183,8 +2262,12 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
       <c r="T11" s="2">
         <v>0</v>
       </c>
@@ -2221,7 +2304,7 @@
       <c r="AE11" s="2">
         <v>0</v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AH11" s="2">
         <v>0</v>
       </c>
       <c r="AI11" s="2">
@@ -2231,12 +2314,12 @@
         <v>0</v>
       </c>
       <c r="AK11" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL11" s="2">
-        <v>9</v>
-      </c>
-      <c r="AM11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="2">
         <v>0</v>
       </c>
       <c r="AP11" s="2">
@@ -2260,7 +2343,7 @@
       <c r="AV11" s="2">
         <v>0</v>
       </c>
-      <c r="AW11" s="2">
+      <c r="AX11" s="2">
         <v>0</v>
       </c>
       <c r="AY11" s="2">
@@ -2269,7 +2352,7 @@
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2319,8 +2402,12 @@
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
       <c r="T12" s="2">
         <v>0</v>
       </c>
@@ -2357,7 +2444,7 @@
       <c r="AE12" s="2">
         <v>0</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AH12" s="2">
         <v>0</v>
       </c>
       <c r="AI12" s="2">
@@ -2370,11 +2457,11 @@
         <v>0</v>
       </c>
       <c r="AL12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="2">
         <v>48</v>
       </c>
+      <c r="AO12" s="2">
+        <v>0</v>
+      </c>
       <c r="AP12" s="2">
         <v>0</v>
       </c>
@@ -2396,7 +2483,7 @@
       <c r="AV12" s="2">
         <v>0</v>
       </c>
-      <c r="AW12" s="2">
+      <c r="AX12" s="2">
         <v>0</v>
       </c>
       <c r="AY12" s="2">
@@ -2405,7 +2492,7 @@
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2455,8 +2542,12 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
       <c r="T13" s="2">
         <v>0</v>
       </c>
@@ -2467,19 +2558,19 @@
         <v>0</v>
       </c>
       <c r="W13" s="2">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="X13" s="2">
+        <v>7700</v>
+      </c>
+      <c r="Y13" s="2">
         <v>8100</v>
       </c>
-      <c r="Y13" s="2">
-        <v>7700</v>
-      </c>
       <c r="Z13" s="2">
-        <v>8100</v>
+        <v>8400</v>
       </c>
       <c r="AA13" s="2">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="2">
         <v>0</v>
@@ -2493,8 +2584,8 @@
       <c r="AE13" s="2">
         <v>0</v>
       </c>
-      <c r="AF13" s="2">
-        <v>0</v>
+      <c r="AH13" s="2">
+        <v>46400</v>
       </c>
       <c r="AI13" s="2">
         <v>46400</v>
@@ -2508,32 +2599,32 @@
       <c r="AL13" s="2">
         <v>46400</v>
       </c>
-      <c r="AM13" s="2">
-        <v>46400</v>
+      <c r="AO13" s="2">
+        <v>8100</v>
       </c>
       <c r="AP13" s="2">
+        <v>7700</v>
+      </c>
+      <c r="AQ13" s="2">
         <v>8100</v>
       </c>
-      <c r="AQ13" s="2">
+      <c r="AR13" s="2">
+        <v>8400</v>
+      </c>
+      <c r="AS13" s="2">
+        <v>8100</v>
+      </c>
+      <c r="AT13" s="2">
         <v>7700</v>
       </c>
-      <c r="AR13" s="2">
+      <c r="AU13" s="2">
         <v>8100</v>
       </c>
-      <c r="AS13" s="2">
+      <c r="AV13" s="2">
         <v>8400</v>
       </c>
-      <c r="AT13" s="2">
-        <v>8100</v>
-      </c>
-      <c r="AU13" s="2">
-        <v>7700</v>
-      </c>
-      <c r="AV13" s="2">
-        <v>8100</v>
-      </c>
-      <c r="AW13" s="2">
-        <v>8400</v>
+      <c r="AX13" s="2">
+        <v>0</v>
       </c>
       <c r="AY13" s="2">
         <v>0</v>
@@ -2541,7 +2632,7 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2591,8 +2682,12 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
       <c r="T14" s="2">
         <v>0</v>
       </c>
@@ -2615,10 +2710,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB14" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="2">
         <v>0</v>
@@ -2629,7 +2724,7 @@
       <c r="AE14" s="2">
         <v>0</v>
       </c>
-      <c r="AF14" s="2">
+      <c r="AH14" s="2">
         <v>0</v>
       </c>
       <c r="AI14" s="2">
@@ -2644,7 +2739,7 @@
       <c r="AL14" s="2">
         <v>0</v>
       </c>
-      <c r="AM14" s="2">
+      <c r="AO14" s="2">
         <v>0</v>
       </c>
       <c r="AP14" s="2">
@@ -2668,7 +2763,7 @@
       <c r="AV14" s="2">
         <v>0</v>
       </c>
-      <c r="AW14" s="2">
+      <c r="AX14" s="2">
         <v>0</v>
       </c>
       <c r="AY14" s="2">
@@ -2677,7 +2772,7 @@
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2727,8 +2822,12 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
       <c r="T15" s="2">
         <v>0</v>
       </c>
@@ -2751,10 +2850,10 @@
         <v>0</v>
       </c>
       <c r="AA15" s="2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" s="2">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="2">
         <v>0</v>
@@ -2765,7 +2864,7 @@
       <c r="AE15" s="2">
         <v>0</v>
       </c>
-      <c r="AF15" s="2">
+      <c r="AH15" s="2">
         <v>0</v>
       </c>
       <c r="AI15" s="2">
@@ -2775,14 +2874,14 @@
         <v>0</v>
       </c>
       <c r="AK15" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL15" s="2">
-        <v>28</v>
-      </c>
-      <c r="AM15" s="2">
         <v>5.32</v>
       </c>
+      <c r="AO15" s="2">
+        <v>0</v>
+      </c>
       <c r="AP15" s="2">
         <v>0</v>
       </c>
@@ -2804,7 +2903,7 @@
       <c r="AV15" s="2">
         <v>0</v>
       </c>
-      <c r="AW15" s="2">
+      <c r="AX15" s="2">
         <v>0</v>
       </c>
       <c r="AY15" s="2">
@@ -2813,7 +2912,7 @@
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2863,8 +2962,12 @@
       <c r="Q16" s="2">
         <v>222090.14300000001</v>
       </c>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
+      <c r="R16" s="2">
+        <v>6341</v>
+      </c>
+      <c r="S16" s="2">
+        <v>222090.14300000001</v>
+      </c>
       <c r="T16" s="2">
         <v>222090.14300000001</v>
       </c>
@@ -2875,22 +2978,22 @@
         <v>222090.14300000001</v>
       </c>
       <c r="W16" s="2">
-        <v>222090.14300000001</v>
+        <v>149988</v>
       </c>
       <c r="X16" s="2">
-        <v>149988</v>
+        <v>128581.8</v>
       </c>
       <c r="Y16" s="2">
-        <v>128581.8</v>
+        <v>126933</v>
       </c>
       <c r="Z16" s="2">
-        <v>126933</v>
+        <v>126088</v>
       </c>
       <c r="AA16" s="2">
-        <v>126088</v>
+        <v>476186.76</v>
       </c>
       <c r="AB16" s="2">
-        <v>476186.76</v>
+        <v>6341</v>
       </c>
       <c r="AC16" s="2">
         <v>6341</v>
@@ -2901,8 +3004,8 @@
       <c r="AE16" s="2">
         <v>6341</v>
       </c>
-      <c r="AF16" s="2">
-        <v>6341</v>
+      <c r="AH16" s="2">
+        <v>66446.94</v>
       </c>
       <c r="AI16" s="2">
         <v>66446.94</v>
@@ -2916,32 +3019,32 @@
       <c r="AL16" s="2">
         <v>66446.94</v>
       </c>
-      <c r="AM16" s="2">
-        <v>66446.94</v>
+      <c r="AO16" s="2">
+        <v>149988</v>
       </c>
       <c r="AP16" s="2">
+        <v>128581.8</v>
+      </c>
+      <c r="AQ16" s="2">
+        <v>126933</v>
+      </c>
+      <c r="AR16" s="2">
+        <v>126088</v>
+      </c>
+      <c r="AS16" s="2">
         <v>149988</v>
       </c>
-      <c r="AQ16" s="2">
+      <c r="AT16" s="2">
         <v>128581.8</v>
       </c>
-      <c r="AR16" s="2">
+      <c r="AU16" s="2">
         <v>126933</v>
       </c>
-      <c r="AS16" s="2">
+      <c r="AV16" s="2">
         <v>126088</v>
       </c>
-      <c r="AT16" s="2">
-        <v>149988</v>
-      </c>
-      <c r="AU16" s="2">
-        <v>128581.8</v>
-      </c>
-      <c r="AV16" s="2">
-        <v>126933</v>
-      </c>
-      <c r="AW16" s="2">
-        <v>126088</v>
+      <c r="AX16" s="2">
+        <v>0</v>
       </c>
       <c r="AY16" s="2">
         <v>0</v>
@@ -2949,7 +3052,7 @@
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2999,8 +3102,12 @@
       <c r="Q17" s="2">
         <v>300</v>
       </c>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
+      <c r="R17" s="2">
+        <v>5</v>
+      </c>
+      <c r="S17" s="2">
+        <v>300</v>
+      </c>
       <c r="T17" s="2">
         <v>300</v>
       </c>
@@ -3011,7 +3118,7 @@
         <v>300</v>
       </c>
       <c r="W17" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
@@ -3023,10 +3130,10 @@
         <v>0</v>
       </c>
       <c r="AA17" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC17" s="2">
         <v>5</v>
@@ -3037,22 +3144,22 @@
       <c r="AE17" s="2">
         <v>5</v>
       </c>
-      <c r="AF17" s="2">
-        <v>5</v>
+      <c r="AH17" s="2">
+        <v>39</v>
       </c>
       <c r="AI17" s="2">
         <v>39</v>
       </c>
       <c r="AJ17" s="2">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="AK17" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL17" s="2">
         <v>0</v>
       </c>
-      <c r="AM17" s="2">
+      <c r="AO17" s="2">
         <v>0</v>
       </c>
       <c r="AP17" s="2">
@@ -3076,16 +3183,16 @@
       <c r="AV17" s="2">
         <v>0</v>
       </c>
-      <c r="AW17" s="2">
+      <c r="AX17" s="2">
         <v>0</v>
       </c>
       <c r="AY17" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3135,8 +3242,12 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
       <c r="T18" s="2">
         <v>0</v>
       </c>
@@ -3173,7 +3284,7 @@
       <c r="AE18" s="2">
         <v>0</v>
       </c>
-      <c r="AF18" s="2">
+      <c r="AH18" s="2">
         <v>0</v>
       </c>
       <c r="AI18" s="2">
@@ -3188,7 +3299,7 @@
       <c r="AL18" s="2">
         <v>0</v>
       </c>
-      <c r="AM18" s="2">
+      <c r="AO18" s="2">
         <v>0</v>
       </c>
       <c r="AP18" s="2">
@@ -3212,7 +3323,7 @@
       <c r="AV18" s="2">
         <v>0</v>
       </c>
-      <c r="AW18" s="2">
+      <c r="AX18" s="2">
         <v>0</v>
       </c>
       <c r="AY18" s="2">
@@ -3221,7 +3332,7 @@
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3271,8 +3382,12 @@
       <c r="Q19" s="2">
         <v>100</v>
       </c>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
+      <c r="R19" s="2">
+        <v>2</v>
+      </c>
+      <c r="S19" s="2">
+        <v>100</v>
+      </c>
       <c r="T19" s="2">
         <v>100</v>
       </c>
@@ -3283,7 +3398,7 @@
         <v>100</v>
       </c>
       <c r="W19" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X19" s="2">
         <v>0</v>
@@ -3298,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AB19" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" s="2">
         <v>2</v>
@@ -3309,8 +3424,8 @@
       <c r="AE19" s="2">
         <v>2</v>
       </c>
-      <c r="AF19" s="2">
-        <v>2</v>
+      <c r="AH19" s="2">
+        <v>0</v>
       </c>
       <c r="AI19" s="2">
         <v>0</v>
@@ -3324,7 +3439,7 @@
       <c r="AL19" s="2">
         <v>0</v>
       </c>
-      <c r="AM19" s="2">
+      <c r="AO19" s="2">
         <v>0</v>
       </c>
       <c r="AP19" s="2">
@@ -3348,7 +3463,7 @@
       <c r="AV19" s="2">
         <v>0</v>
       </c>
-      <c r="AW19" s="2">
+      <c r="AX19" s="2">
         <v>0</v>
       </c>
       <c r="AY19" s="2">
@@ -3357,7 +3472,7 @@
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3411,8 +3526,12 @@
       <c r="Q20" s="2">
         <v>200</v>
       </c>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
+      <c r="R20" s="2">
+        <v>27</v>
+      </c>
+      <c r="S20" s="2">
+        <v>200</v>
+      </c>
       <c r="T20" s="2">
         <v>200</v>
       </c>
@@ -3423,22 +3542,22 @@
         <v>200</v>
       </c>
       <c r="W20" s="2">
-        <v>200</v>
+        <v>790</v>
       </c>
       <c r="X20" s="2">
+        <v>780</v>
+      </c>
+      <c r="Y20" s="2">
         <v>790</v>
       </c>
-      <c r="Y20" s="2">
-        <v>780</v>
-      </c>
       <c r="Z20" s="2">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="AA20" s="2">
-        <v>800</v>
+        <v>147.69</v>
       </c>
       <c r="AB20" s="2">
-        <v>147.69</v>
+        <v>27</v>
       </c>
       <c r="AC20" s="2">
         <v>27</v>
@@ -3449,8 +3568,8 @@
       <c r="AE20" s="2">
         <v>27</v>
       </c>
-      <c r="AF20" s="2">
-        <v>27</v>
+      <c r="AH20" s="2">
+        <v>0</v>
       </c>
       <c r="AI20" s="2">
         <v>0</v>
@@ -3464,40 +3583,40 @@
       <c r="AL20" s="2">
         <v>0</v>
       </c>
-      <c r="AM20" s="2">
-        <v>0</v>
+      <c r="AO20" s="2">
+        <v>790</v>
       </c>
       <c r="AP20" s="2">
+        <v>780</v>
+      </c>
+      <c r="AQ20" s="2">
         <v>790</v>
       </c>
-      <c r="AQ20" s="2">
+      <c r="AR20" s="2">
+        <v>800</v>
+      </c>
+      <c r="AS20" s="2">
+        <v>790</v>
+      </c>
+      <c r="AT20" s="2">
         <v>780</v>
       </c>
-      <c r="AR20" s="2">
+      <c r="AU20" s="2">
         <v>790</v>
       </c>
-      <c r="AS20" s="2">
+      <c r="AV20" s="2">
         <v>800</v>
       </c>
-      <c r="AT20" s="2">
-        <v>790</v>
-      </c>
-      <c r="AU20" s="2">
-        <v>780</v>
-      </c>
-      <c r="AV20" s="2">
-        <v>790</v>
-      </c>
-      <c r="AW20" s="2">
-        <v>800</v>
+      <c r="AX20" s="2">
+        <v>3761</v>
       </c>
       <c r="AY20" s="2">
-        <v>3761</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3547,8 +3666,12 @@
       <c r="Q21" s="2">
         <v>250</v>
       </c>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>250</v>
+      </c>
       <c r="T21" s="2">
         <v>250</v>
       </c>
@@ -3559,22 +3682,22 @@
         <v>250</v>
       </c>
       <c r="W21" s="2">
-        <v>250</v>
+        <v>109</v>
       </c>
       <c r="X21" s="2">
+        <v>99</v>
+      </c>
+      <c r="Y21" s="2">
         <v>109</v>
       </c>
-      <c r="Y21" s="2">
-        <v>99</v>
-      </c>
       <c r="Z21" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AA21" s="2">
-        <v>119</v>
+        <v>70.8</v>
       </c>
       <c r="AB21" s="2">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="2">
         <v>0</v>
@@ -3585,8 +3708,8 @@
       <c r="AE21" s="2">
         <v>0</v>
       </c>
-      <c r="AF21" s="2">
-        <v>0</v>
+      <c r="AH21" s="2">
+        <v>200</v>
       </c>
       <c r="AI21" s="2">
         <v>200</v>
@@ -3600,40 +3723,40 @@
       <c r="AL21" s="2">
         <v>200</v>
       </c>
-      <c r="AM21" s="2">
-        <v>200</v>
+      <c r="AO21" s="2">
+        <v>109</v>
       </c>
       <c r="AP21" s="2">
+        <v>99</v>
+      </c>
+      <c r="AQ21" s="2">
         <v>109</v>
       </c>
-      <c r="AQ21" s="2">
+      <c r="AR21" s="2">
+        <v>119</v>
+      </c>
+      <c r="AS21" s="2">
+        <v>109</v>
+      </c>
+      <c r="AT21" s="2">
         <v>99</v>
       </c>
-      <c r="AR21" s="2">
+      <c r="AU21" s="2">
         <v>109</v>
       </c>
-      <c r="AS21" s="2">
+      <c r="AV21" s="2">
         <v>119</v>
       </c>
-      <c r="AT21" s="2">
-        <v>109</v>
-      </c>
-      <c r="AU21" s="2">
-        <v>99</v>
-      </c>
-      <c r="AV21" s="2">
-        <v>109</v>
-      </c>
-      <c r="AW21" s="2">
-        <v>119</v>
+      <c r="AX21" s="2">
+        <v>7.5</v>
       </c>
       <c r="AY21" s="2">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3683,8 +3806,12 @@
       <c r="Q22" s="2">
         <v>0</v>
       </c>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
       <c r="T22" s="2">
         <v>0</v>
       </c>
@@ -3695,73 +3822,73 @@
         <v>0</v>
       </c>
       <c r="W22" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="X22" s="2">
+        <v>12</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>51</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="2">
         <v>28</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="AP22" s="2">
         <v>12</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="AQ22" s="2">
         <v>186</v>
       </c>
-      <c r="AA22" s="2">
+      <c r="AR22" s="2">
         <v>51</v>
       </c>
-      <c r="AB22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="2">
+      <c r="AS22" s="2">
         <v>28</v>
       </c>
-      <c r="AQ22" s="2">
+      <c r="AT22" s="2">
         <v>12</v>
       </c>
-      <c r="AR22" s="2">
+      <c r="AU22" s="2">
         <v>186</v>
       </c>
-      <c r="AS22" s="2">
+      <c r="AV22" s="2">
         <v>51</v>
       </c>
-      <c r="AT22" s="2">
-        <v>28</v>
-      </c>
-      <c r="AU22" s="2">
-        <v>12</v>
-      </c>
-      <c r="AV22" s="2">
-        <v>186</v>
-      </c>
-      <c r="AW22" s="2">
-        <v>51</v>
+      <c r="AX22" s="2">
+        <v>0</v>
       </c>
       <c r="AY22" s="2">
         <v>0</v>
@@ -3769,7 +3896,7 @@
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>686.375</v>
@@ -3823,8 +3950,12 @@
       <c r="Q23" s="2">
         <v>0</v>
       </c>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
+      <c r="R23" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0</v>
+      </c>
       <c r="T23" s="2">
         <v>0</v>
       </c>
@@ -3835,22 +3966,22 @@
         <v>0</v>
       </c>
       <c r="W23" s="2">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="X23" s="2">
-        <v>340</v>
+        <v>430</v>
       </c>
       <c r="Y23" s="2">
-        <v>430</v>
+        <v>240</v>
       </c>
       <c r="Z23" s="2">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="AA23" s="2">
-        <v>440</v>
+        <v>1297.4000000000001</v>
       </c>
       <c r="AB23" s="2">
-        <v>1297.4000000000001</v>
+        <v>15.75</v>
       </c>
       <c r="AC23" s="2">
         <v>15.75</v>
@@ -3861,55 +3992,55 @@
       <c r="AE23" s="2">
         <v>15.75</v>
       </c>
-      <c r="AF23" s="2">
-        <v>15.75</v>
+      <c r="AH23" s="2">
+        <v>1.3</v>
       </c>
       <c r="AI23" s="2">
         <v>1.3</v>
       </c>
       <c r="AJ23" s="2">
-        <v>1.3</v>
+        <v>16</v>
       </c>
       <c r="AK23" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL23" s="2">
         <v>0</v>
       </c>
-      <c r="AM23" s="2">
-        <v>0</v>
+      <c r="AO23" s="2">
+        <v>340</v>
       </c>
       <c r="AP23" s="2">
+        <v>430</v>
+      </c>
+      <c r="AQ23" s="2">
+        <v>240</v>
+      </c>
+      <c r="AR23" s="2">
+        <v>440</v>
+      </c>
+      <c r="AS23" s="2">
         <v>340</v>
       </c>
-      <c r="AQ23" s="2">
+      <c r="AT23" s="2">
         <v>430</v>
       </c>
-      <c r="AR23" s="2">
+      <c r="AU23" s="2">
         <v>240</v>
       </c>
-      <c r="AS23" s="2">
+      <c r="AV23" s="2">
         <v>440</v>
       </c>
-      <c r="AT23" s="2">
-        <v>340</v>
-      </c>
-      <c r="AU23" s="2">
-        <v>430</v>
-      </c>
-      <c r="AV23" s="2">
-        <v>240</v>
-      </c>
-      <c r="AW23" s="2">
-        <v>440</v>
+      <c r="AX23" s="2">
+        <v>1145</v>
       </c>
       <c r="AY23" s="2">
-        <v>1145</v>
+        <v>541</v>
       </c>
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3959,8 +4090,12 @@
       <c r="Q24" s="2">
         <v>0</v>
       </c>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
       <c r="T24" s="2">
         <v>0</v>
       </c>
@@ -3983,10 +4118,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="2">
         <v>0</v>
@@ -3997,7 +4132,7 @@
       <c r="AE24" s="2">
         <v>0</v>
       </c>
-      <c r="AF24" s="2">
+      <c r="AH24" s="2">
         <v>0</v>
       </c>
       <c r="AI24" s="2">
@@ -4012,7 +4147,7 @@
       <c r="AL24" s="2">
         <v>0</v>
       </c>
-      <c r="AM24" s="2">
+      <c r="AO24" s="2">
         <v>0</v>
       </c>
       <c r="AP24" s="2">
@@ -4036,16 +4171,16 @@
       <c r="AV24" s="2">
         <v>0</v>
       </c>
-      <c r="AW24" s="2">
-        <v>0</v>
+      <c r="AX24" s="2">
+        <v>100</v>
       </c>
       <c r="AY24" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4095,8 +4230,12 @@
       <c r="Q25" s="2">
         <v>0</v>
       </c>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>0</v>
+      </c>
       <c r="T25" s="2">
         <v>0</v>
       </c>
@@ -4107,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="2">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="X25" s="2">
         <v>4600</v>
@@ -4119,7 +4258,7 @@
         <v>4600</v>
       </c>
       <c r="AA25" s="2">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="2">
         <v>0</v>
@@ -4133,8 +4272,8 @@
       <c r="AE25" s="2">
         <v>0</v>
       </c>
-      <c r="AF25" s="2">
-        <v>0</v>
+      <c r="AH25" s="2">
+        <v>8600</v>
       </c>
       <c r="AI25" s="2">
         <v>8600</v>
@@ -4148,8 +4287,8 @@
       <c r="AL25" s="2">
         <v>8600</v>
       </c>
-      <c r="AM25" s="2">
-        <v>8600</v>
+      <c r="AO25" s="2">
+        <v>4600</v>
       </c>
       <c r="AP25" s="2">
         <v>4600</v>
@@ -4172,8 +4311,8 @@
       <c r="AV25" s="2">
         <v>4600</v>
       </c>
-      <c r="AW25" s="2">
-        <v>4600</v>
+      <c r="AX25" s="2">
+        <v>0</v>
       </c>
       <c r="AY25" s="2">
         <v>0</v>
@@ -4181,7 +4320,7 @@
     </row>
     <row r="26" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4231,8 +4370,12 @@
       <c r="Q26" s="2">
         <v>0</v>
       </c>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>0</v>
+      </c>
       <c r="T26" s="2">
         <v>0</v>
       </c>
@@ -4243,73 +4386,73 @@
         <v>0</v>
       </c>
       <c r="W26" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="2">
         <v>9</v>
       </c>
-      <c r="Y26" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="2">
+      <c r="AP26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="2">
         <v>35</v>
       </c>
-      <c r="AA26" s="2">
+      <c r="AR26" s="2">
         <v>4</v>
       </c>
-      <c r="AB26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="2">
+      <c r="AS26" s="2">
         <v>9</v>
       </c>
-      <c r="AQ26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="2">
+      <c r="AT26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU26" s="2">
         <v>35</v>
       </c>
-      <c r="AS26" s="2">
+      <c r="AV26" s="2">
         <v>4</v>
       </c>
-      <c r="AT26" s="2">
-        <v>9</v>
-      </c>
-      <c r="AU26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV26" s="2">
-        <v>35</v>
-      </c>
-      <c r="AW26" s="2">
-        <v>4</v>
+      <c r="AX26" s="2">
+        <v>0</v>
       </c>
       <c r="AY26" s="2">
         <v>0</v>
@@ -4317,110 +4460,114 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2">
+        <v>0</v>
+      </c>
+      <c r="W27" s="2">
+        <v>0</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="2">
         <v>61</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2">
-        <v>0</v>
-      </c>
-      <c r="U27" s="2">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2">
-        <v>0</v>
-      </c>
-      <c r="W27" s="2">
-        <v>0</v>
-      </c>
-      <c r="X27" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="2">
-        <v>0</v>
-      </c>
       <c r="AL27" s="2">
-        <v>61</v>
-      </c>
-      <c r="AM27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="2">
         <v>0</v>
       </c>
       <c r="AP27" s="2">
@@ -4444,7 +4591,7 @@
       <c r="AV27" s="2">
         <v>0</v>
       </c>
-      <c r="AW27" s="2">
+      <c r="AX27" s="2">
         <v>0</v>
       </c>
       <c r="AY27" s="2">
@@ -4453,7 +4600,7 @@
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4503,8 +4650,12 @@
       <c r="Q28" s="2">
         <v>0</v>
       </c>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>0</v>
+      </c>
       <c r="T28" s="2">
         <v>0</v>
       </c>
@@ -4541,24 +4692,24 @@
       <c r="AE28" s="2">
         <v>0</v>
       </c>
-      <c r="AF28" s="2">
-        <v>0</v>
+      <c r="AH28" s="2">
+        <v>4000</v>
       </c>
       <c r="AI28" s="2">
         <v>4000</v>
       </c>
       <c r="AJ28" s="2">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="2">
         <v>0</v>
       </c>
       <c r="AL28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="2">
         <v>150</v>
       </c>
+      <c r="AO28" s="2">
+        <v>0</v>
+      </c>
       <c r="AP28" s="2">
         <v>0</v>
       </c>
@@ -4580,7 +4731,7 @@
       <c r="AV28" s="2">
         <v>0</v>
       </c>
-      <c r="AW28" s="2">
+      <c r="AX28" s="2">
         <v>0</v>
       </c>
       <c r="AY28" s="2">
@@ -4589,7 +4740,7 @@
     </row>
     <row r="29" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29">
         <v>475</v>
@@ -4639,8 +4790,12 @@
       <c r="Q29" s="2">
         <v>0</v>
       </c>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <v>0</v>
+      </c>
       <c r="T29" s="2">
         <v>0</v>
       </c>
@@ -4663,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="AA29" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AB29" s="2">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="2">
         <v>0</v>
@@ -4677,11 +4832,11 @@
       <c r="AE29" s="2">
         <v>0</v>
       </c>
-      <c r="AF29" s="2">
-        <v>0</v>
+      <c r="AH29" s="2">
+        <v>30</v>
       </c>
       <c r="AI29" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ29" s="2">
         <v>0</v>
@@ -4692,7 +4847,7 @@
       <c r="AL29" s="2">
         <v>0</v>
       </c>
-      <c r="AM29" s="2">
+      <c r="AO29" s="2">
         <v>0</v>
       </c>
       <c r="AP29" s="2">
@@ -4716,7 +4871,7 @@
       <c r="AV29" s="2">
         <v>0</v>
       </c>
-      <c r="AW29" s="2">
+      <c r="AX29" s="2">
         <v>0</v>
       </c>
       <c r="AY29" s="2">
@@ -4725,7 +4880,7 @@
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4775,8 +4930,12 @@
       <c r="Q30" s="2">
         <v>0</v>
       </c>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <v>0</v>
+      </c>
       <c r="T30" s="2">
         <v>0</v>
       </c>
@@ -4813,7 +4972,7 @@
       <c r="AE30" s="2">
         <v>0</v>
       </c>
-      <c r="AF30" s="2">
+      <c r="AH30" s="2">
         <v>0</v>
       </c>
       <c r="AI30" s="2">
@@ -4828,7 +4987,7 @@
       <c r="AL30" s="2">
         <v>0</v>
       </c>
-      <c r="AM30" s="2">
+      <c r="AO30" s="2">
         <v>0</v>
       </c>
       <c r="AP30" s="2">
@@ -4852,7 +5011,7 @@
       <c r="AV30" s="2">
         <v>0</v>
       </c>
-      <c r="AW30" s="2">
+      <c r="AX30" s="2">
         <v>0</v>
       </c>
       <c r="AY30" s="2">
@@ -4861,7 +5020,7 @@
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4911,8 +5070,12 @@
       <c r="Q31" s="2">
         <v>0</v>
       </c>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>0</v>
+      </c>
       <c r="T31" s="2">
         <v>0</v>
       </c>
@@ -4949,22 +5112,22 @@
       <c r="AE31" s="2">
         <v>0</v>
       </c>
-      <c r="AF31" s="2">
+      <c r="AH31" s="2">
         <v>0</v>
       </c>
       <c r="AI31" s="2">
         <v>0</v>
       </c>
       <c r="AJ31" s="2">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK31" s="2">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="AL31" s="2">
         <v>0</v>
       </c>
-      <c r="AM31" s="2">
+      <c r="AO31" s="2">
         <v>0</v>
       </c>
       <c r="AP31" s="2">
@@ -4988,7 +5151,7 @@
       <c r="AV31" s="2">
         <v>0</v>
       </c>
-      <c r="AW31" s="2">
+      <c r="AX31" s="2">
         <v>0</v>
       </c>
       <c r="AY31" s="2">
@@ -4997,7 +5160,7 @@
     </row>
     <row r="32" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5047,8 +5210,12 @@
       <c r="Q32" s="2">
         <v>0</v>
       </c>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
       <c r="T32" s="2">
         <v>0</v>
       </c>
@@ -5059,73 +5226,73 @@
         <v>0</v>
       </c>
       <c r="W32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>7</v>
+      </c>
+      <c r="Z32" s="2">
         <v>1</v>
       </c>
-      <c r="Y32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="2">
+      <c r="AA32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="2">
         <v>7</v>
       </c>
-      <c r="AA32" s="2">
+      <c r="AR32" s="2">
         <v>1</v>
-      </c>
-      <c r="AB32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR32" s="2">
-        <v>7</v>
       </c>
       <c r="AS32" s="2">
         <v>1</v>
       </c>
       <c r="AT32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU32" s="2">
+        <v>7</v>
+      </c>
+      <c r="AV32" s="2">
         <v>1</v>
       </c>
-      <c r="AU32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV32" s="2">
-        <v>7</v>
-      </c>
-      <c r="AW32" s="2">
-        <v>1</v>
+      <c r="AX32" s="2">
+        <v>0</v>
       </c>
       <c r="AY32" s="2">
         <v>0</v>
@@ -5133,7 +5300,7 @@
     </row>
     <row r="33" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -5183,8 +5350,12 @@
       <c r="Q33" s="2">
         <v>0</v>
       </c>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>0</v>
+      </c>
       <c r="T33" s="2">
         <v>0</v>
       </c>
@@ -5207,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="AA33" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB33" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="2">
         <v>0</v>
@@ -5221,8 +5392,8 @@
       <c r="AE33" s="2">
         <v>0</v>
       </c>
-      <c r="AF33" s="2">
-        <v>0</v>
+      <c r="AH33" s="2">
+        <v>332</v>
       </c>
       <c r="AI33" s="2">
         <v>332</v>
@@ -5236,8 +5407,8 @@
       <c r="AL33" s="2">
         <v>332</v>
       </c>
-      <c r="AM33" s="2">
-        <v>332</v>
+      <c r="AO33" s="2">
+        <v>0</v>
       </c>
       <c r="AP33" s="2">
         <v>0</v>
@@ -5260,16 +5431,16 @@
       <c r="AV33" s="2">
         <v>0</v>
       </c>
-      <c r="AW33" s="2">
+      <c r="AX33" s="2">
         <v>0</v>
       </c>
       <c r="AY33" s="2">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -5319,8 +5490,12 @@
       <c r="Q34" s="2">
         <v>0</v>
       </c>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
       <c r="T34" s="2">
         <v>0</v>
       </c>
@@ -5343,10 +5518,10 @@
         <v>0</v>
       </c>
       <c r="AA34" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB34" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC34" s="2">
         <v>0</v>
@@ -5357,7 +5532,7 @@
       <c r="AE34" s="2">
         <v>0</v>
       </c>
-      <c r="AF34" s="2">
+      <c r="AH34" s="2">
         <v>0</v>
       </c>
       <c r="AI34" s="2">
@@ -5372,7 +5547,7 @@
       <c r="AL34" s="2">
         <v>0</v>
       </c>
-      <c r="AM34" s="2">
+      <c r="AO34" s="2">
         <v>0</v>
       </c>
       <c r="AP34" s="2">
@@ -5396,7 +5571,7 @@
       <c r="AV34" s="2">
         <v>0</v>
       </c>
-      <c r="AW34" s="2">
+      <c r="AX34" s="2">
         <v>0</v>
       </c>
       <c r="AY34" s="2">
@@ -5405,7 +5580,7 @@
     </row>
     <row r="35" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -5455,8 +5630,12 @@
       <c r="Q35" s="2">
         <v>0</v>
       </c>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>0</v>
+      </c>
       <c r="T35" s="2">
         <v>0</v>
       </c>
@@ -5479,10 +5658,10 @@
         <v>0</v>
       </c>
       <c r="AA35" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB35" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC35" s="2">
         <v>0</v>
@@ -5493,7 +5672,7 @@
       <c r="AE35" s="2">
         <v>0</v>
       </c>
-      <c r="AF35" s="2">
+      <c r="AH35" s="2">
         <v>0</v>
       </c>
       <c r="AI35" s="2">
@@ -5508,7 +5687,7 @@
       <c r="AL35" s="2">
         <v>0</v>
       </c>
-      <c r="AM35" s="2">
+      <c r="AO35" s="2">
         <v>0</v>
       </c>
       <c r="AP35" s="2">
@@ -5532,16 +5711,16 @@
       <c r="AV35" s="2">
         <v>0</v>
       </c>
-      <c r="AW35" s="2">
-        <v>0</v>
+      <c r="AX35" s="2">
+        <v>100</v>
       </c>
       <c r="AY35" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -5591,8 +5770,12 @@
       <c r="Q36" s="2">
         <v>0</v>
       </c>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>0</v>
+      </c>
       <c r="T36" s="2">
         <v>0</v>
       </c>
@@ -5615,10 +5798,10 @@
         <v>0</v>
       </c>
       <c r="AA36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" s="2">
         <v>0</v>
@@ -5629,7 +5812,7 @@
       <c r="AE36" s="2">
         <v>0</v>
       </c>
-      <c r="AF36" s="2">
+      <c r="AH36" s="2">
         <v>0</v>
       </c>
       <c r="AI36" s="2">
@@ -5644,7 +5827,7 @@
       <c r="AL36" s="2">
         <v>0</v>
       </c>
-      <c r="AM36" s="2">
+      <c r="AO36" s="2">
         <v>0</v>
       </c>
       <c r="AP36" s="2">
@@ -5668,7 +5851,7 @@
       <c r="AV36" s="2">
         <v>0</v>
       </c>
-      <c r="AW36" s="2">
+      <c r="AX36" s="2">
         <v>0</v>
       </c>
       <c r="AY36" s="2">
@@ -5677,7 +5860,7 @@
     </row>
     <row r="37" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5727,8 +5910,12 @@
       <c r="Q37" s="2">
         <v>400</v>
       </c>
-      <c r="R37" s="2"/>
-      <c r="S37" s="2"/>
+      <c r="R37" s="2">
+        <v>20</v>
+      </c>
+      <c r="S37" s="2">
+        <v>400</v>
+      </c>
       <c r="T37" s="2">
         <v>400</v>
       </c>
@@ -5739,7 +5926,7 @@
         <v>400</v>
       </c>
       <c r="W37" s="2">
-        <v>400</v>
+        <v>5500</v>
       </c>
       <c r="X37" s="2">
         <v>5500</v>
@@ -5751,10 +5938,10 @@
         <v>5500</v>
       </c>
       <c r="AA37" s="2">
-        <v>5500</v>
+        <v>48</v>
       </c>
       <c r="AB37" s="2">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="AC37" s="2">
         <v>20</v>
@@ -5765,8 +5952,8 @@
       <c r="AE37" s="2">
         <v>20</v>
       </c>
-      <c r="AF37" s="2">
-        <v>20</v>
+      <c r="AH37" s="2">
+        <v>1400</v>
       </c>
       <c r="AI37" s="2">
         <v>1400</v>
@@ -5780,8 +5967,8 @@
       <c r="AL37" s="2">
         <v>1400</v>
       </c>
-      <c r="AM37" s="2">
-        <v>1400</v>
+      <c r="AO37" s="2">
+        <v>5500</v>
       </c>
       <c r="AP37" s="2">
         <v>5500</v>
@@ -5804,16 +5991,16 @@
       <c r="AV37" s="2">
         <v>5500</v>
       </c>
-      <c r="AW37" s="2">
-        <v>5500</v>
+      <c r="AX37" s="2">
+        <v>0</v>
       </c>
       <c r="AY37" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5863,8 +6050,12 @@
       <c r="Q38" s="2">
         <v>0</v>
       </c>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
       <c r="T38" s="2">
         <v>0</v>
       </c>
@@ -5887,10 +6078,10 @@
         <v>0</v>
       </c>
       <c r="AA38" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AB38" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AC38" s="2">
         <v>0</v>
@@ -5901,7 +6092,7 @@
       <c r="AE38" s="2">
         <v>0</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>0</v>
       </c>
       <c r="AI38" s="2">
@@ -5916,7 +6107,7 @@
       <c r="AL38" s="2">
         <v>0</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>0</v>
       </c>
       <c r="AP38" s="2">
@@ -5940,7 +6131,7 @@
       <c r="AV38" s="2">
         <v>0</v>
       </c>
-      <c r="AW38" s="2">
+      <c r="AX38" s="2">
         <v>0</v>
       </c>
       <c r="AY38" s="2">
@@ -5949,172 +6140,195 @@
     </row>
     <row r="39" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="G39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H39" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="I39" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="J39" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="K39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="L39" s="5" t="s">
+      <c r="O39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="P39" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="M39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="P39" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="Q39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
+        <v>95</v>
+      </c>
+      <c r="R39" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="S39" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="T39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="V39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AA39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AC39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AD39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AE39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF39" s="5" t="s">
-        <v>96</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="AF39" s="5"/>
       <c r="AG39" s="5"/>
-      <c r="AH39" s="5"/>
+      <c r="AH39" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="AI39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AJ39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AL39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM39" s="5" t="s">
-        <v>96</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
-      <c r="AO39" s="5"/>
+      <c r="AO39" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="AP39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AQ39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AR39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AS39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AT39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AU39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AV39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW39" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="AX39" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AY39" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B41" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C43" s="6" t="s">
         <v>1</v>
       </c>
+      <c r="E43" s="11"/>
+      <c r="F43" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="44" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C44">
         <v>204</v>
       </c>
+      <c r="E44" s="12"/>
+      <c r="F44" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="45" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C45">
         <v>0</v>
       </c>
+      <c r="E45" s="13"/>
+      <c r="F45" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="46" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C46">
         <v>0</v>
+      </c>
+      <c r="E46" s="6"/>
+      <c r="F46" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:51" x14ac:dyDescent="0.2">
@@ -6295,6 +6509,9 @@
     <hyperlink ref="J39" r:id="rId8" display="https://www.nature.com/articles/s41893-025-01762-y" xr:uid="{069DC490-9768-6741-9B5C-1AAC50907017}"/>
     <hyperlink ref="N39" r:id="rId9" display="https://www.nature.com/articles/s41893-025-01762-y" xr:uid="{5CEA5A1A-5D40-C447-B1BD-B8E562B9E2C5}"/>
     <hyperlink ref="P39" r:id="rId10" display="https://www.nature.com/articles/s41893-025-01762-y" xr:uid="{6D456945-D935-5649-AA83-1FEA0599D304}"/>
+    <hyperlink ref="I39" r:id="rId11" xr:uid="{4DF49132-E07F-1B4F-A69F-29C41A4291B5}"/>
+    <hyperlink ref="AY39" r:id="rId12" xr:uid="{2B8D170B-C5DB-2640-B397-04CA63B94443}"/>
+    <hyperlink ref="AX39" r:id="rId13" display="https://www.nature.com/articles/s41893-025-01762-y" xr:uid="{AB75886F-B02E-F54B-9813-86994AEA9833}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/critical_materials/excel_files/technologies_elec_mi.xlsx
+++ b/projects/critical_materials/excel_files/technologies_elec_mi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DBF1C3-BF2D-9E45-B825-BF0B60F3C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9537526-06F4-264B-90E9-5C731915B7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="36380" windowHeight="19540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="107">
   <si>
     <t>AFC</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>CCGT considered</t>
+  </si>
+  <si>
+    <t>Moss et al., 2013</t>
   </si>
 </sst>
 </file>
@@ -1186,6 +1189,9 @@
       <c r="AL3" s="2">
         <v>10953</v>
       </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
       <c r="AO3" s="2">
         <v>700</v>
       </c>
@@ -1326,6 +1332,9 @@
       <c r="AL4" s="2">
         <v>0</v>
       </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
       <c r="AO4" s="2">
         <v>0</v>
       </c>
@@ -1466,6 +1475,9 @@
       <c r="AL5" s="2">
         <v>0</v>
       </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
       <c r="AO5" s="2">
         <v>0</v>
       </c>
@@ -1610,6 +1622,9 @@
       <c r="AL6" s="2">
         <v>3761</v>
       </c>
+      <c r="AN6">
+        <v>310</v>
+      </c>
       <c r="AO6" s="2">
         <v>525</v>
       </c>
@@ -1752,6 +1767,9 @@
       <c r="AL7" s="2">
         <v>0</v>
       </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
       <c r="AO7" s="2">
         <v>0</v>
       </c>
@@ -1892,6 +1910,9 @@
       <c r="AL8" s="2">
         <v>60700</v>
       </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
       <c r="AO8" s="2">
         <v>369000</v>
       </c>
@@ -2039,6 +2060,9 @@
       <c r="AL9" s="2">
         <v>3187.82</v>
       </c>
+      <c r="AN9">
+        <v>5000</v>
+      </c>
       <c r="AO9" s="2">
         <v>5000</v>
       </c>
@@ -2179,6 +2203,9 @@
       <c r="AL10" s="2">
         <v>0</v>
       </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
       <c r="AO10" s="2">
         <v>6</v>
       </c>
@@ -2319,6 +2346,9 @@
       <c r="AL11" s="2">
         <v>0</v>
       </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
       <c r="AO11" s="2">
         <v>0</v>
       </c>
@@ -2459,6 +2489,9 @@
       <c r="AL12" s="2">
         <v>48</v>
       </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
       <c r="AO12" s="2">
         <v>0</v>
       </c>
@@ -2599,6 +2632,9 @@
       <c r="AL13" s="2">
         <v>46400</v>
       </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
       <c r="AO13" s="2">
         <v>8100</v>
       </c>
@@ -2739,6 +2775,9 @@
       <c r="AL14" s="2">
         <v>0</v>
       </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
       <c r="AO14" s="2">
         <v>0</v>
       </c>
@@ -2879,6 +2918,9 @@
       <c r="AL15" s="2">
         <v>5.32</v>
       </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
       <c r="AO15" s="2">
         <v>0</v>
       </c>
@@ -3019,6 +3061,9 @@
       <c r="AL16" s="2">
         <v>66446.94</v>
       </c>
+      <c r="AN16">
+        <v>45000</v>
+      </c>
       <c r="AO16" s="2">
         <v>149988</v>
       </c>
@@ -3159,6 +3204,9 @@
       <c r="AL17" s="2">
         <v>0</v>
       </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
       <c r="AO17" s="2">
         <v>0</v>
       </c>
@@ -3299,6 +3347,9 @@
       <c r="AL18" s="2">
         <v>0</v>
       </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
       <c r="AO18" s="2">
         <v>0</v>
       </c>
@@ -3439,6 +3490,9 @@
       <c r="AL19" s="2">
         <v>0</v>
       </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
       <c r="AO19" s="2">
         <v>0</v>
       </c>
@@ -3583,6 +3637,9 @@
       <c r="AL20" s="2">
         <v>0</v>
       </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
       <c r="AO20" s="2">
         <v>790</v>
       </c>
@@ -3723,6 +3780,9 @@
       <c r="AL21" s="2">
         <v>200</v>
       </c>
+      <c r="AN21">
+        <v>50</v>
+      </c>
       <c r="AO21" s="2">
         <v>109</v>
       </c>
@@ -3863,6 +3923,9 @@
       <c r="AL22" s="2">
         <v>0</v>
       </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
       <c r="AO22" s="2">
         <v>28</v>
       </c>
@@ -4007,6 +4070,9 @@
       <c r="AL23" s="2">
         <v>0</v>
       </c>
+      <c r="AN23">
+        <v>220</v>
+      </c>
       <c r="AO23" s="2">
         <v>340</v>
       </c>
@@ -4147,6 +4213,9 @@
       <c r="AL24" s="2">
         <v>0</v>
       </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
       <c r="AO24" s="2">
         <v>0</v>
       </c>
@@ -4287,6 +4356,9 @@
       <c r="AL25" s="2">
         <v>8600</v>
       </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
       <c r="AO25" s="2">
         <v>4600</v>
       </c>
@@ -4427,6 +4499,9 @@
       <c r="AL26" s="2">
         <v>0</v>
       </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
       <c r="AO26" s="2">
         <v>9</v>
       </c>
@@ -4567,6 +4642,9 @@
       <c r="AL27" s="2">
         <v>0</v>
       </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
       <c r="AO27" s="2">
         <v>0</v>
       </c>
@@ -4707,6 +4785,9 @@
       <c r="AL28" s="2">
         <v>150</v>
       </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
       <c r="AO28" s="2">
         <v>0</v>
       </c>
@@ -4847,6 +4928,9 @@
       <c r="AL29" s="2">
         <v>0</v>
       </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
       <c r="AO29" s="2">
         <v>0</v>
       </c>
@@ -4987,6 +5071,9 @@
       <c r="AL30" s="2">
         <v>0</v>
       </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
       <c r="AO30" s="2">
         <v>0</v>
       </c>
@@ -5127,6 +5214,9 @@
       <c r="AL31" s="2">
         <v>0</v>
       </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
       <c r="AO31" s="2">
         <v>0</v>
       </c>
@@ -5267,6 +5357,9 @@
       <c r="AL32" s="2">
         <v>0</v>
       </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
       <c r="AO32" s="2">
         <v>1</v>
       </c>
@@ -5407,6 +5500,9 @@
       <c r="AL33" s="2">
         <v>332</v>
       </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
       <c r="AO33" s="2">
         <v>0</v>
       </c>
@@ -5547,6 +5643,9 @@
       <c r="AL34" s="2">
         <v>0</v>
       </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
       <c r="AO34" s="2">
         <v>0</v>
       </c>
@@ -5687,6 +5786,9 @@
       <c r="AL35" s="2">
         <v>0</v>
       </c>
+      <c r="AN35">
+        <v>0</v>
+      </c>
       <c r="AO35" s="2">
         <v>0</v>
       </c>
@@ -5827,6 +5929,9 @@
       <c r="AL36" s="2">
         <v>0</v>
       </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
       <c r="AO36" s="2">
         <v>0</v>
       </c>
@@ -5967,6 +6072,9 @@
       <c r="AL37" s="2">
         <v>1400</v>
       </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
       <c r="AO37" s="2">
         <v>5500</v>
       </c>
@@ -6105,6 +6213,9 @@
         <v>0</v>
       </c>
       <c r="AL38" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN38">
         <v>0</v>
       </c>
       <c r="AO38" s="2">
@@ -6247,7 +6358,9 @@
         <v>95</v>
       </c>
       <c r="AM39" s="5"/>
-      <c r="AN39" s="5"/>
+      <c r="AN39" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="AO39" s="5" t="s">
         <v>95</v>
       </c>
@@ -6512,6 +6625,7 @@
     <hyperlink ref="I39" r:id="rId11" xr:uid="{4DF49132-E07F-1B4F-A69F-29C41A4291B5}"/>
     <hyperlink ref="AY39" r:id="rId12" xr:uid="{2B8D170B-C5DB-2640-B397-04CA63B94443}"/>
     <hyperlink ref="AX39" r:id="rId13" display="https://www.nature.com/articles/s41893-025-01762-y" xr:uid="{AB75886F-B02E-F54B-9813-86994AEA9833}"/>
+    <hyperlink ref="AN39" r:id="rId14" xr:uid="{A52B59C2-1E36-7942-B171-029362D009D2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
